--- a/academias/Biología - Estadisticos 20221.xlsx
+++ b/academias/Biología - Estadisticos 20221.xlsx
@@ -528,13 +528,13 @@
         <v>4.55</v>
       </c>
       <c r="I2" s="2">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>4.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -548,19 +548,19 @@
         <v>25</v>
       </c>
       <c r="D3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F3">
         <v>3</v>
       </c>
       <c r="G3" s="1">
-        <v>91.43000000000001</v>
+        <v>91.67</v>
       </c>
       <c r="H3" s="1">
-        <v>8.57</v>
+        <v>8.33</v>
       </c>
       <c r="I3" s="2">
         <v>8.4</v>
@@ -569,7 +569,7 @@
         <v>3</v>
       </c>
       <c r="K3" s="1">
-        <v>8.57</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -796,19 +796,19 @@
         <v>41</v>
       </c>
       <c r="E10">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>97.56</v>
+        <v>100</v>
       </c>
       <c r="H10" s="1">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -831,25 +831,25 @@
         <v>39</v>
       </c>
       <c r="E11">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>92.31</v>
+        <v>94.87</v>
       </c>
       <c r="H11" s="1">
-        <v>7.69</v>
+        <v>5.13</v>
       </c>
       <c r="I11" s="2">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>5.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -863,19 +863,19 @@
         <v>25</v>
       </c>
       <c r="D12">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E12">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F12">
         <v>4</v>
       </c>
       <c r="G12" s="1">
-        <v>87.5</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>12.5</v>
+        <v>12.9</v>
       </c>
       <c r="I12" s="2">
         <v>8.300000000000001</v>
@@ -982,13 +982,13 @@
         <v>25</v>
       </c>
       <c r="D3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -997,7 +997,7 @@
         <v>100</v>
       </c>
       <c r="J3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K3" s="1">
         <v>100</v>
@@ -1017,22 +1017,25 @@
         <v>27</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F4">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>9.199999999999999</v>
       </c>
       <c r="J4">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1049,22 +1052,25 @@
         <v>38</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F5">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>5.26</v>
+      </c>
+      <c r="I5" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J5">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1081,22 +1087,25 @@
         <v>26</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F6">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>3.85</v>
+      </c>
+      <c r="I6" s="2">
+        <v>8.1</v>
       </c>
       <c r="J6">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1113,22 +1122,25 @@
         <v>32</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F7">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>96.88</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>3.13</v>
+      </c>
+      <c r="I7" s="2">
+        <v>8.800000000000001</v>
       </c>
       <c r="J7">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1145,22 +1157,25 @@
         <v>15</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F8">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I8" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J8">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1177,22 +1192,25 @@
         <v>32</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F9">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>96.88</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>3.13</v>
+      </c>
+      <c r="I9" s="2">
+        <v>8.800000000000001</v>
       </c>
       <c r="J9">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1209,22 +1227,25 @@
         <v>41</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F10">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>97.56</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>2.44</v>
+      </c>
+      <c r="I10" s="2">
+        <v>9.699999999999999</v>
       </c>
       <c r="J10">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1241,22 +1262,25 @@
         <v>39</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F11">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>97.44</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>2.56</v>
+      </c>
+      <c r="I11" s="2">
+        <v>9.4</v>
       </c>
       <c r="J11">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1270,25 +1294,28 @@
         <v>25</v>
       </c>
       <c r="D12">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F12">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>9.68</v>
+      </c>
+      <c r="I12" s="2">
+        <v>8.5</v>
       </c>
       <c r="J12">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1369,13 +1396,13 @@
         <v>4.55</v>
       </c>
       <c r="I2" s="2">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>4.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1389,19 +1416,19 @@
         <v>25</v>
       </c>
       <c r="D3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F3">
         <v>3</v>
       </c>
       <c r="G3" s="1">
-        <v>91.43000000000001</v>
+        <v>91.67</v>
       </c>
       <c r="H3" s="1">
-        <v>8.57</v>
+        <v>8.33</v>
       </c>
       <c r="I3" s="2">
         <v>8.4</v>
@@ -1410,7 +1437,7 @@
         <v>3</v>
       </c>
       <c r="K3" s="1">
-        <v>8.57</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1462,19 +1489,19 @@
         <v>38</v>
       </c>
       <c r="E5">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F5">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>81.58</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>18.42</v>
+        <v>5.26</v>
       </c>
       <c r="I5" s="2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1497,19 +1524,19 @@
         <v>26</v>
       </c>
       <c r="E6">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>84.62</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>15.38</v>
+        <v>3.85</v>
       </c>
       <c r="I6" s="2">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1532,19 +1559,19 @@
         <v>32</v>
       </c>
       <c r="E7">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F7">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>81.25</v>
+        <v>96.88</v>
       </c>
       <c r="H7" s="1">
-        <v>18.75</v>
+        <v>3.13</v>
       </c>
       <c r="I7" s="2">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1567,19 +1594,19 @@
         <v>15</v>
       </c>
       <c r="E8">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>86.67</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>13.33</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1602,19 +1629,19 @@
         <v>32</v>
       </c>
       <c r="E9">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>96.88</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1649,7 +1676,7 @@
         <v>2.44</v>
       </c>
       <c r="I10" s="2">
-        <v>9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1672,25 +1699,25 @@
         <v>39</v>
       </c>
       <c r="E11">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G11" s="1">
-        <v>92.31</v>
+        <v>97.44</v>
       </c>
       <c r="H11" s="1">
-        <v>7.69</v>
+        <v>2.56</v>
       </c>
       <c r="I11" s="2">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="J11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>5.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1704,22 +1731,22 @@
         <v>25</v>
       </c>
       <c r="D12">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E12">
         <v>28</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G12" s="1">
-        <v>87.5</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>12.5</v>
+        <v>9.68</v>
       </c>
       <c r="I12" s="2">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J12">
         <v>0</v>

--- a/academias/Biología - Estadisticos 20221.xlsx
+++ b/academias/Biología - Estadisticos 20221.xlsx
@@ -953,22 +953,25 @@
         <v>44</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F2">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>95.45</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>4.55</v>
+      </c>
+      <c r="I2" s="2">
+        <v>8.5</v>
       </c>
       <c r="J2">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1204,13 +1207,13 @@
         <v>3.13</v>
       </c>
       <c r="I9" s="2">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1629,16 +1632,16 @@
         <v>32</v>
       </c>
       <c r="E9">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>100</v>
+        <v>96.88</v>
       </c>
       <c r="H9" s="1">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="I9" s="2">
         <v>8.5</v>

--- a/academias/Biología - Estadisticos 20221.xlsx
+++ b/academias/Biología - Estadisticos 20221.xlsx
@@ -988,22 +988,25 @@
         <v>36</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F3">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>83.33</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>16.67</v>
+      </c>
+      <c r="I3" s="2">
+        <v>6.8</v>
       </c>
       <c r="J3">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1422,19 +1425,19 @@
         <v>36</v>
       </c>
       <c r="E3">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G3" s="1">
-        <v>91.67</v>
+        <v>83.33</v>
       </c>
       <c r="H3" s="1">
-        <v>8.33</v>
+        <v>16.67</v>
       </c>
       <c r="I3" s="2">
-        <v>8.4</v>
+        <v>7.7</v>
       </c>
       <c r="J3">
         <v>3</v>

--- a/academias/Biología - Estadisticos 20221.xlsx
+++ b/academias/Biología - Estadisticos 20221.xlsx
@@ -563,13 +563,13 @@
         <v>8.33</v>
       </c>
       <c r="I3" s="2">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1000,13 +1000,13 @@
         <v>16.67</v>
       </c>
       <c r="I3" s="2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1437,13 +1437,13 @@
         <v>16.67</v>
       </c>
       <c r="I3" s="2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">

--- a/academias/Biología - Estadisticos 20221.xlsx
+++ b/academias/Biología - Estadisticos 20221.xlsx
@@ -1682,7 +1682,7 @@
         <v>2.44</v>
       </c>
       <c r="I10" s="2">
-        <v>9.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1705,19 +1705,19 @@
         <v>39</v>
       </c>
       <c r="E11">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>97.44</v>
+        <v>94.87</v>
       </c>
       <c r="H11" s="1">
-        <v>2.56</v>
+        <v>5.13</v>
       </c>
       <c r="I11" s="2">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="J11">
         <v>0</v>

--- a/academias/Biología - Estadisticos 20221.xlsx
+++ b/academias/Biología - Estadisticos 20221.xlsx
@@ -1425,19 +1425,19 @@
         <v>36</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G3" s="1">
-        <v>83.33</v>
+        <v>69.44</v>
       </c>
       <c r="H3" s="1">
-        <v>16.67</v>
+        <v>30.56</v>
       </c>
       <c r="I3" s="2">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1635,19 +1635,19 @@
         <v>32</v>
       </c>
       <c r="E9">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G9" s="1">
-        <v>96.88</v>
+        <v>84.38</v>
       </c>
       <c r="H9" s="1">
-        <v>3.13</v>
+        <v>15.63</v>
       </c>
       <c r="I9" s="2">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1740,19 +1740,19 @@
         <v>31</v>
       </c>
       <c r="E12">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G12" s="1">
-        <v>90.31999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>9.68</v>
+        <v>12.9</v>
       </c>
       <c r="I12" s="2">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="J12">
         <v>0</v>

--- a/academias/Biología - Estadisticos 20221.xlsx
+++ b/academias/Biología - Estadisticos 20221.xlsx
@@ -1472,7 +1472,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1507,7 +1507,7 @@
         <v>5.26</v>
       </c>
       <c r="I5" s="2">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1577,7 +1577,7 @@
         <v>3.13</v>
       </c>
       <c r="I7" s="2">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1612,7 +1612,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J8">
         <v>0</v>

--- a/academias/Biología - Estadisticos 20221.xlsx
+++ b/academias/Biología - Estadisticos 20221.xlsx
@@ -1402,7 +1402,7 @@
         <v>4.55</v>
       </c>
       <c r="I2" s="2">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J2">
         <v>0</v>
